--- a/04.검수문서/테스트시나리오.xlsx
+++ b/04.검수문서/테스트시나리오.xlsx
@@ -7,9 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스트 케이스 목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스트 케이스 상세" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트 케이스 목록'!$A$1:$F$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트 케이스 상세'!$A$1:$I$83</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,11 +31,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -39,11 +67,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,13 +109,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -425,2979 +522,6858 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+          <t>테스트 시나리오</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>부모님 위치 확인 서비스 (안심맵, AnsimMap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>문서 번호</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>DOC-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>문서 버전</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>작성일</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>참조 문서</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>기능명세서.md (v1.0)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TC-ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>기능 ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>테스트명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>사전조건</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>테스트단계</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>query</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>상태</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>TC-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>F-001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>정상 회원가입</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>중복 번호 회원가입 시도</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>TC-002-1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>구글 계정 중복 연동/가입 시도</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>잘못된 번호 형식 입력</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>약관 미동의 상태에서 가입 시도</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>정상 로그인</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>미가입 번호 로그인 시도</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>잘못된 번호 형식으로 로그인 시도</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>정상 가족 그룹 생성</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>그룹명 미입력 상태에서 생성 시도</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>초대 코드로 정상 그룹 참여</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>유효하지 않은 초대 코드 입력</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TC-011-1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>초대 링크(/join?code=)를 통한 자동 가입 및 랜딩</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TC-011-2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>데모 유저 또는 미가입 상태에서 초대 링크 복사 차단</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>5명 정원 초과 그룹 참여 시도</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>이미 참여 중인 그룹 재참여 시도</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>온보딩 4단계 정상 완료</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>온보딩 중간 이탈 후 재접속 시 이어서 진행</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 거부 후 부모님 화면 진입</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 수집 필수 동의 정상 처리</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>브라우저 위치 권한 거부</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>필수 항목 미동의 상태에서 확인 버튼 활성화 여부</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>F-007</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 동의 정상 처리</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>F-007</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 미동의 시 가입 버튼 비활성화</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TC-022</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 정상 철회</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>동의 철회 시 서버 에러 발생</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>정상 조건에서 GPS 위치 30초 간격 전송</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Geolocation 권한 거부 시 위치 공유 OFF 전환</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>GPS 정확도 불량 (accuracy &gt; 100m) 데이터 처리</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>네트워크 단절 시 로컬 큐 저장 및 재연결 후 전송</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 ON → OFF 전환</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 OFF → ON 전환</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>동의 철회 상태에서 ON 전환 시도</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>실시간 지도에서 부모님 위치 마커 정상 표시</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 OFF 상태에서 지도 표시</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>마지막 위치 수신 후 5분 경과 시 마커 처리</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>카카오맵 SDK 로드 실패 시 에러 화면 표시</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>F-012</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>날짜 선택 후 위치 이력 정상 조회</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>F-012</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>7일 초과 날짜 선택 시도</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>F-012</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>위치 데이터 없는 날짜 조회</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>F-013</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>GPS 좌표 역지오코딩 정상 변환</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TC-039</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>F-013</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>역지오코딩 API 호출 실패 시 대체 텍스트 표시</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>F-014</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>SOS 버튼 탭 시 카운트다운 오버레이 표시</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>F-014</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 미완료 상태에서 SOS 발송</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>F-015</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2초 카운트다운 종료 후 SOS 발송 실행</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>F-015</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>카운트다운 중 취소 버튼 탭</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>F-015</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>카운트다운 중 화면 이탈 시 취소 처리</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>SOS 확정 시 가족 전원 FCM 알림 정상 발송</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>FCM 토큰 만료 토큰 발송 처리</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>SOS 발송 중 네트워크 오류 발생</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>위치 정보 없는 상태에서 SOS 발송</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TC-049</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>F-017</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>SOS 알림 탭 후 전화 연결 화면 이동</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>F-017</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>앱 종료 상태에서 SOS 알림 탭 후 재접속</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>가족 채팅방 메시지 정상 전송 및 수신</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>500자 초과 메시지 전송 시도</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>WebSocket 5회 재연결 실패 시 안내 배너 표시</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>이미지/파일 전송 시도 시 안내 메시지 표시</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TC-055</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>채팅방 미접속 구성원에게 FCM 푸시 알림 발송</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>TC-056</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>채팅방 접속 중인 구성원에게 FCM 알림 미발송 확인</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>F-020</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>안전 구역 정상 설정</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>TC-058</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>F-020</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Free 플랜 구역 한도 초과 등록 시도</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TC-059</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>F-020</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>중심점 미지정 상태에서 저장 시도</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>TC-060</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>F-021</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>부모님 안전 구역 이탈 감지 및 알림 발송</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TC-061</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>F-021</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>부모님 안전 구역 복귀 감지 및 알림 발송</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>TC-062</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>F-021</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>GPS 오차로 인한 경계 근처 진동 방지 처리</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>F-022</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>관리자 그룹 목록 정상 조회</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>F-022</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>비관리자 계정으로 관리자 화면 접근 시도</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>F-022</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>등록 그룹 없는 상태에서 목록 조회</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>F-023</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>특정 그룹 상세 정보 정상 조회</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>F-023</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>존재하지 않는 그룹 ID로 상세 조회 시도</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>F-024</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>관리자 SMS 정상 발송</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>F-024</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>수신 대상 미선택 상태에서 발송 시도</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>F-024</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>NHN Cloud SMS API 오류 시 처리</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>F-025</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>관리자 카카오 알림톡 정상 발송</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>F-025</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>월 발송 한도 초과 시 처리</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>F-025</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>알림톡 발송 실패 건 재발송</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>F-026</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>관리자 통계 대시보드 정상 조회</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>F-026</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>데이터 없는 기간 통계 조회</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>F-026</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>통계 데이터 CSV 내보내기</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>F-027</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>배터리 절약 모드 전환 (30초 → 3분)</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>F-027</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>일반 모드 전환 (3분 → 30초)</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>F-028</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 페이지 정상 접근</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F83"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TC-ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>테스트명</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>관련 기능</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>사전 조건</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>테스트 단계</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>입력 데이터</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>실제 결과</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>정상 회원가입</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>서비스에 미가입 상태의 휴대폰 번호 준비</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면 접속&lt;br&gt;2. 휴대폰 번호 입력 (010-1234-5678)&lt;br&gt;3. 역할 선택 (가족 구성원)&lt;br&gt;4. 서비스 이용약관 및 개인정보처리방침 동의 체크&lt;br&gt;5. 가입 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 접속
+2. 휴대폰 번호 입력 (010-1234-5678)
+3. 역할 선택 (가족 구성원)
+4. 서비스 이용약관 및 개인정보처리방침 동의 체크
+5. 가입 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>번호: 01012345678 / 역할: family / 약관 동의: true</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>가입 완료 화면으로 전환 / JWT 세션 쿠키 저장 / 역할에 따라 가족 화면으로 이동</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>TC-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>중복 번호 회원가입 시도</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>F-001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>중복 번호 회원가입 시도</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>동일 번호로 이미 가입된 계정이 DB에 존재</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면 접속&lt;br&gt;2. 기존 가입 번호 입력 (010-1234-5678)&lt;br&gt;3. 역할 선택 및 약관 동의 체크&lt;br&gt;4. 가입 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 접속
+2. 기존 가입 번호 입력 (010-1234-5678)
+3. 역할 선택 및 약관 동의 체크
+4. 가입 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>번호: 01012345678 (기존 가입 번호)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>"이미 가입된 번호입니다. 로그인해 주세요." 토스트 메시지 표시 / 가입 미처리</t>
         </is>
       </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>TC-002-1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>구글 계정 중복 연동/가입 시도</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>이미 연동된 구글 계정이 DB에 존재</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 접속
+2. 하단의 구글 소셜 로그인 버튼 탭
+3. 이미 가입/연동된 구글 계정으로 로그인 시도</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>연동된 구글 계정</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>"이미 연동된 구글 계정입니다. 로그인 탭을 이용해주세요." 상단 에러 배너 표시 / 가입 미처리</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TC-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>잘못된 번호 형식 입력</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>F-001</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>잘못된 번호 형식 입력</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>회원가입 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면 접속&lt;br&gt;2. 잘못된 형식의 번호 입력 (010-123-456)&lt;br&gt;3. 가입 버튼 탭 시도</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 접속
+2. 잘못된 형식의 번호 입력 (010-123-456)
+3. 가입 버튼 탭 시도</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>번호: 010123456 (9자리 숫자)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>입력 필드 하단 인라인 에러 메시지 표시 / 가입 미처리</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TC-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>약관 미동의 상태에서 가입 시도</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>F-001</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>약관 미동의 상태에서 가입 시도</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>회원가입 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면 접속&lt;br&gt;2. 번호 및 역할 입력&lt;br&gt;3. 약관 동의 체크 하지 않음&lt;br&gt;4. 가입 버튼 상태 확인</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 접속
+2. 번호 및 역할 입력
+3. 약관 동의 체크 하지 않음
+4. 가입 버튼 상태 확인</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>번호: 01012345678 / 약관 동의: false</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>가입 버튼 비활성화 유지 / 탭해도 요청 미전송</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TC-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>정상 로그인</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>정상 로그인</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>해당 번호로 가입된 계정이 존재</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1. 로그인 화면 접속&lt;br&gt;2. 가입된 휴대폰 번호 입력&lt;br&gt;3. 로그인 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1. 로그인 화면 접속
+2. 가입된 휴대폰 번호 입력
+3. 로그인 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>번호: 01012345678 (가입된 번호)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>JWT 토큰 갱신 / 역할에 따라 부모님 화면 또는 가족 화면으로 이동</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TC-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>미가입 번호 로그인 시도</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>미가입 번호 로그인 시도</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>입력할 번호가 DB에 미등록 상태</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1. 로그인 화면 접속&lt;br&gt;2. 미가입 번호 입력&lt;br&gt;3. 로그인 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1. 로그인 화면 접속
+2. 미가입 번호 입력
+3. 로그인 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>번호: 01099999999 (미가입 번호)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>"등록되지 않은 번호입니다. 회원가입을 진행해 주세요." 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TC-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>잘못된 번호 형식으로 로그인 시도</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>잘못된 번호 형식으로 로그인 시도</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>로그인 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1. 로그인 화면 접속&lt;br&gt;2. 형식 오류 번호 입력 (숫자 외 문자 포함)&lt;br&gt;3. 로그인 버튼 탭 시도</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1. 로그인 화면 접속
+2. 형식 오류 번호 입력 (숫자 외 문자 포함)
+3. 로그인 버튼 탭 시도</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>번호: 010-ABCD-5678</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>인라인 에러 메시지 표시 / 로그인 요청 미전송</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TC-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>정상 가족 그룹 생성</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>F-003</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>정상 가족 그룹 생성</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>가족 구성원(family) 역할로 로그인 상태</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1. 그룹 생성 화면 접속&lt;br&gt;2. 그룹명 입력 (예: "우리 가족")&lt;br&gt;3. 생성 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. 그룹 생성 화면 접속
+2. 그룹명 입력 (예: "우리 가족")
+3. 생성 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>그룹명: "우리 가족" (5자)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>그룹 상세 화면으로 이동 / 6자리 초대 코드 및 QR 코드 표시 / groups 테이블에 레코드 생성</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC-009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>그룹명 미입력 상태에서 생성 시도</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>F-003</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>그룹명 미입력 상태에서 생성 시도</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>가족 구성원(family) 역할로 로그인 상태</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1. 그룹 생성 화면 접속&lt;br&gt;2. 그룹명 입력하지 않음&lt;br&gt;3. 생성 버튼 상태 확인</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1. 그룹 생성 화면 접속
+2. 그룹명 입력하지 않음
+3. 생성 버튼 상태 확인</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>그룹명: "" (공백)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>생성 버튼 비활성화 / 탭해도 API 요청 미전송</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC-010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>초대 코드로 정상 그룹 참여</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>초대 코드로 정상 그룹 참여</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>유효한 6자리 초대 코드가 발급된 그룹 존재 (구성원 5명 미만) / 미참여 계정으로 로그인</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1. 코드 입력 화면 접속&lt;br&gt;2. 유효한 6자리 초대 코드 입력&lt;br&gt;3. 참여 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1. 코드 입력 화면 접속
+2. 유효한 6자리 초대 코드 입력
+3. 참여 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>초대 코드: "ABC123" (유효한 코드)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>가족 화면(Family View) 진입 / 그룹 지도 화면 표시 / group_members 테이블에 member 역할로 추가</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC-011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>유효하지 않은 초대 코드 입력</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>유효하지 않은 초대 코드 입력</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>로그인 상태</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1. 코드 입력 화면 접속&lt;br&gt;2. 존재하지 않는 코드 입력&lt;br&gt;3. 참여 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1. 코드 입력 화면 접속
+2. 존재하지 않는 코드 입력
+3. 참여 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>초대 코드: "ZZZZZZ" (미존재 코드)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>"초대 코드를 다시 확인해 주세요." 안내 메시지 표시 / 그룹 참여 미처리</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TC-011-1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>초대 링크(/join?code=)를 통한 자동 가입 및 랜딩</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>미가입 상태 / 유효한 그룹 초대 코드 확보</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1. 전달받은 초대 링크(`.../join?code=XXXXXX`) 클릭
+2. 회원가입 또는 로그인 완료
+3. 랜딩 화면 및 처리 확인</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>접속 URL: `/join?code=ABC123`</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>가입/로그인 직후 백그라운드에서 자동 그룹 참여 처리 / 성공 시 부모님 유무에 따라 안심맵 또는 가족설정 화면으로 자동 라우팅</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TC-011-2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>데모 유저 또는 미가입 상태에서 초대 링크 복사 차단</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>그룹에 속하지 않거나 데모(Demo) 계정으로 가족설정 화면 접속</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1. 가족설정 화면의 '가족 구성원 초대하기' 버튼 또는 링크 탭
+2. 클립보드 복사 시도</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>그룹 미존재 상태</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>"가족 그룹을 먼저 생성해주세요" 토스트 발생 / 클립보드 복사 중단 (에러 핸들링)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC-012</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>5명 정원 초과 그룹 참여 시도</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5명 정원 초과 그룹 참여 시도</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>해당 그룹에 이미 5명의 구성원이 존재</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1. 코드 입력 화면 접속&lt;br&gt;2. 5명 정원이 찬 그룹의 초대 코드 입력&lt;br&gt;3. 참여 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1. 코드 입력 화면 접속
+2. 5명 정원이 찬 그룹의 초대 코드 입력
+3. 참여 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>초대 코드: 5명 가득 찬 그룹의 코드</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>"그룹 인원이 가득 찼습니다." 안내 메시지 표시 / 참여 미처리</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC-013</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>이미 참여 중인 그룹 재참여 시도</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>이미 참여 중인 그룹 재참여 시도</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>해당 그룹에 이미 참여한 계정으로 로그인</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1. 코드 입력 화면 접속&lt;br&gt;2. 기존 참여 중인 그룹의 초대 코드 입력&lt;br&gt;3. 참여 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1. 코드 입력 화면 접속
+2. 기존 참여 중인 그룹의 초대 코드 입력
+3. 참여 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>초대 코드: 이미 참여 중인 그룹 코드</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>"이미 참여한 그룹입니다." 안내 메시지 표시 / 중복 참여 미처리</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC-014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>온보딩 4단계 정상 완료</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>F-005</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>온보딩 4단계 정상 완료</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>자녀가 부모님 단말기를 조작 중 / 유효한 초대 코드 준비</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1. 온보딩 1단계: 부모님 번호 입력 및 역할 선택 (parent 고정)&lt;br&gt;2. 2단계: 그룹 초대 코드 입력&lt;br&gt;3. 3단계: 위치정보 동의 화면 확인 및 부모님 본인 동의 완료&lt;br&gt;4. 4단계: 동의 완료 후 부모님 메인 화면 진입</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1. 온보딩 1단계: 부모님 번호 입력 및 역할 선택 (parent 고정)
+2. 2단계: 그룹 초대 코드 입력
+3. 3단계: 위치정보 동의 화면 확인 및 부모님 본인 동의 완료
+4. 4단계: 동의 완료 후 부모님 메인 화면 진입</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>부모님 번호: 01056781234 / 초대 코드: "ABC123" / 동의: true</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>부모님 메인 화면(SOS 버튼 중심) 정상 진입 / 위치 공유 활성 상태</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC-015</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>온보딩 중간 이탈 후 재접속 시 이어서 진행</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>F-005</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>온보딩 중간 이탈 후 재접속 시 이어서 진행</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>온보딩 2단계까지 진행한 상태</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1. 온보딩 2단계까지 진행&lt;br&gt;2. 브라우저 탭 닫기 (이탈)&lt;br&gt;3. 동일 URL로 재접속</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1. 온보딩 2단계까지 진행
+2. 브라우저 탭 닫기 (이탈)
+3. 동일 URL로 재접속</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>localStorage에 저장된 온보딩 진행 상태</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>재접속 시 2단계부터 이어서 진행 / localStorage에 진행 상태 복원</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC-016</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 거부 후 부모님 화면 진입</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>F-005</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>위치정보 동의 거부 후 부모님 화면 진입</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>온보딩 3단계(위치정보 동의 화면)까지 진행</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1. 온보딩 3단계 위치정보 동의 화면 표시&lt;br&gt;2. 동의 체크 없이 또는 거부 선택&lt;br&gt;3. 화면 이동 확인</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>1. 온보딩 3단계 위치정보 동의 화면 표시
+2. 동의 체크 없이 또는 거부 선택
+3. 화면 이동 확인</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>동의: false</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>위치 공유 비활성 상태로 부모님 화면 진입 / 동의 유도 배너 표시</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC-017</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 수집 필수 동의 정상 처리</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>위치정보 수집 필수 동의 정상 처리</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>부모님 단말기에서 위치정보 동의 화면 표시 상태</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1. 위치정보 동의 화면 접속&lt;br&gt;2. 필수 항목 (위치정보 수집·이용 동의) 체크&lt;br&gt;3. 확인 버튼 탭&lt;br&gt;4. 브라우저 Geolocation 권한 요청 프롬프트에서 허용 선택</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치정보 동의 화면 접속
+2. 필수 항목 (위치정보 수집·이용 동의) 체크
+3. 확인 버튼 탭
+4. 브라우저 Geolocation 권한 요청 프롬프트에서 허용 선택</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>필수 동의: true / 브라우저 위치 권한: 허용</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>location_consents 테이블에 동의 이력 저장 / 위치 공유 활성화 / 부모님 메인 화면 진입</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC-018</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>브라우저 위치 권한 거부</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>브라우저 위치 권한 거부</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>위치정보 동의 화면에서 필수 항목 동의 후 브라우저 권한 요청 단계</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1. 위치정보 동의 화면에서 필수 항목 체크&lt;br&gt;2. 확인 버튼 탭&lt;br&gt;3. 브라우저 위치 권한 요청 프롬프트에서 거부 선택</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치정보 동의 화면에서 필수 항목 체크
+2. 확인 버튼 탭
+3. 브라우저 위치 권한 요청 프롬프트에서 거부 선택</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>필수 동의: true / 브라우저 위치 권한: 거부</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>"위치 권한을 허용해야 서비스를 이용할 수 있습니다." 안내 메시지 + 설정 방법 가이드 링크 표시</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC-019</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>필수 항목 미동의 상태에서 확인 버튼 활성화 여부</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>필수 항목 미동의 상태에서 확인 버튼 활성화 여부</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>위치정보 동의 화면 표시 상태</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1. 위치정보 동의 화면 접속&lt;br&gt;2. 필수 항목 체크 없이 확인 버튼 확인</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치정보 동의 화면 접속
+2. 필수 항목 체크 없이 확인 버튼 확인</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>필수 동의: false</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>확인 버튼 비활성화 / 탭해도 동의 처리 미실행</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC-020</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 동의 정상 처리</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>F-007</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>개인정보처리방침 동의 정상 처리</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>회원가입 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면에서 개인정보처리방침 동의 항목 확인&lt;br&gt;2. 동의 체크 선택&lt;br&gt;3. 가입 버튼 활성화 여부 확인</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면에서 개인정보처리방침 동의 항목 확인
+2. 동의 체크 선택
+3. 가입 버튼 활성화 여부 확인</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>개인정보처리방침 동의: true</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>privacy_agreed_at 저장 / 가입 버튼 활성화</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC-021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 미동의 시 가입 버튼 비활성화</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>F-007</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>개인정보처리방침 미동의 시 가입 버튼 비활성화</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>회원가입 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면에서 번호 및 역할 입력&lt;br&gt;2. 개인정보처리방침 동의 체크 없이 가입 버튼 확인</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면에서 번호 및 역할 입력
+2. 개인정보처리방침 동의 체크 없이 가입 버튼 확인</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>개인정보처리방침 동의: false</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>가입 버튼 비활성화 유지</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC-022</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 정상 철회</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>F-008</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>위치정보 동의 정상 철회</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>부모님 계정으로 로그인 / 위치정보 동의 완료 상태</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1. 부모님 설정 화면 접속&lt;br&gt;2. 위치정보 동의 철회 버튼 탭&lt;br&gt;3. 확인 다이얼로그에서 승인 탭</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 설정 화면 접속
+2. 위치정보 동의 철회 버튼 탭
+3. 확인 다이얼로그에서 승인 탭</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>철회 확인: true</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>위치 공유 OFF 상태 전환 / 가족 화면 지도에서 부모님 마커 제거 / 가족 구성원 전원에게 FCM 알림 발송 ("부모님께서 위치 공유를 중단했습니다.")</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC-023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>동의 철회 시 서버 에러 발생</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>F-008</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>동의 철회 시 서버 에러 발생</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>부모님 계정으로 로그인 / DELETE /api/location/consent API 강제 500 응답 설정</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1. 설정 화면에서 동의 철회 버튼 탭&lt;br&gt;2. 확인 다이얼로그 승인&lt;br&gt;3. 서버 에러 응답 확인</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1. 설정 화면에서 동의 철회 버튼 탭
+2. 확인 다이얼로그 승인
+3. 서버 에러 응답 확인</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>서버 응답: 500 Internal Server Error</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>철회 실패 토스트 메시지 표시 / 위치 수집 상태 유지 (철회 미처리)</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC-024</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>정상 조건에서 GPS 위치 30초 간격 전송</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>F-009</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>정상 조건에서 GPS 위치 30초 간격 전송</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 위치정보 동의 완료 / 위치 공유 ON / 브라우저 Geolocation 권한 허용</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1. 부모님 메인 화면 접속&lt;br&gt;2. 30초 대기&lt;br&gt;3. API 서버 locations 테이블에 데이터 저장 확인&lt;br&gt;4. 가족 화면 지도의 마커 갱신 확인</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 메인 화면 접속
+2. 30초 대기
+3. API 서버 locations 테이블에 데이터 저장 확인
+4. 가족 화면 지도의 마커 갱신 확인</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>위도: 37.5665, 경도: 126.9780, 정확도: 15m</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>30초 간격으로 위치 데이터 전송 / locations 테이블 업데이트 / 가족 화면 마커 실시간 갱신</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC-025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Geolocation 권한 거부 시 위치 공유 OFF 전환</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>F-009</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Geolocation 권한 거부 시 위치 공유 OFF 전환</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>부모님 메인 화면 접속 상태 / 브라우저 위치 권한 거부 상태</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1. 브라우저 설정에서 위치 권한 거부 처리&lt;br&gt;2. 부모님 메인 화면 접속&lt;br&gt;3. 화면 상태 확인</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1. 브라우저 설정에서 위치 권한 거부 처리
+2. 부모님 메인 화면 접속
+3. 화면 상태 확인</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>브라우저 Geolocation 권한: 거부</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>위치 공유 OFF 상태로 전환 / 권한 허용 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC-026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>GPS 정확도 불량 (accuracy &gt; 100m) 데이터 처리</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>F-009</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GPS 정확도 불량 (accuracy &gt; 100m) 데이터 처리</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>GPS 정확도를 임의로 낮게 설정 가능한 테스트 환경</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1. Geolocation API에서 accuracy &gt; 100m 인 데이터 수신 시뮬레이션&lt;br&gt;2. 서버 저장 여부 확인&lt;br&gt;3. 가족 화면 마커 상태 확인</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>1. Geolocation API에서 accuracy &gt; 100m 인 데이터 수신 시뮬레이션
+2. 서버 저장 여부 확인
+3. 가족 화면 마커 상태 확인</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>위도: 37.5665, 경도: 126.9780, 정확도: 150m</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>해당 데이터 저장 제외 / 마지막 정상 위치 마커 유지</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC-027</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>네트워크 단절 시 로컬 큐 저장 및 재연결 후 전송</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>F-009</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>네트워크 단절 시 로컬 큐 저장 및 재연결 후 전송</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>부모님 메인 화면 접속 상태 / 위치 전송 중</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1. 네트워크 연결 차단 (브라우저 오프라인 모드)&lt;br&gt;2. 30초 간격으로 5회 위치 발생 대기&lt;br&gt;3. 네트워크 재연결&lt;br&gt;4. 서버 수신 데이터 확인</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>1. 네트워크 연결 차단 (브라우저 오프라인 모드)
+2. 30초 간격으로 5회 위치 발생 대기
+3. 네트워크 재연결
+4. 서버 수신 데이터 확인</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>네트워크 상태: 오프라인 → 온라인 전환</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>오프라인 중 최대 5건 로컬 큐 저장 / 재연결 후 큐에 저장된 데이터 일괄 전송</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TC-028</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 ON → OFF 전환</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>F-010</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>위치 공유 ON → OFF 전환</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 위치 공유 ON 상태</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1. 부모님 메인 화면에서 위치 공유 토글 확인 (현재 ON)&lt;br&gt;2. 토글 탭 (ON → OFF)&lt;br&gt;3. UI 변경 및 가족 알림 확인</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 메인 화면에서 위치 공유 토글 확인 (현재 ON)
+2. 토글 탭 (ON → OFF)
+3. UI 변경 및 가족 알림 확인</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>토글 액션: ON → OFF</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>토글 UI 즉시 OFF로 변경 / "공유 꺼짐" 텍스트 표시 / 가족 전원에게 FCM 알림 발송 / Geolocation watchPosition 해제</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>TC-029</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 OFF → ON 전환</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>F-010</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>위치 공유 OFF → ON 전환</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 위치 공유 OFF 상태 / 위치정보 동의 완료 상태</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1. 부모님 메인 화면에서 위치 공유 토글 확인 (현재 OFF)&lt;br&gt;2. 토글 탭 (OFF → ON)&lt;br&gt;3. UI 변경 및 위치 전송 재시작 확인</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 메인 화면에서 위치 공유 토글 확인 (현재 OFF)
+2. 토글 탭 (OFF → ON)
+3. UI 변경 및 위치 전송 재시작 확인</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>토글 액션: OFF → ON</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>토글 UI 즉시 ON으로 변경 / "공유 중" 텍스트 표시 / Geolocation watchPosition 재등록 / 가족 전원에게 FCM 알림 발송</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TC-030</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>동의 철회 상태에서 ON 전환 시도</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>F-010</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>동의 철회 상태에서 ON 전환 시도</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 위치정보 동의 철회 상태</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1. 위치 공유 토글이 OFF 상태 확인&lt;br&gt;2. 토글 ON 전환 시도</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치 공유 토글이 OFF 상태 확인
+2. 토글 ON 전환 시도</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>위치정보 동의 상태: 철회</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>"위치정보 동의가 필요합니다." 안내 메시지 표시 / 위치정보 동의 화면(F-006)으로 이동</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>TC-031</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>실시간 지도에서 부모님 위치 마커 정상 표시</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>F-011</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>실시간 지도에서 부모님 위치 마커 정상 표시</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>가족 구성원 계정으로 로그인 / 부모님이 위치 공유 ON 상태 / WebSocket 연결</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1. 가족 메인 화면 접속&lt;br&gt;2. 카카오맵 로드 확인&lt;br&gt;3. 부모님 위치 마커 표시 확인&lt;br&gt;4. 마커 탭 시 오버레이 표시 확인</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>1. 가족 메인 화면 접속
+2. 카카오맵 로드 확인
+3. 부모님 위치 마커 표시 확인
+4. 마커 탭 시 오버레이 표시 확인</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>WebSocket 수신 위치: 위도 37.5665, 경도 126.9780</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>카카오맵에 부모님 위치 마커 실시간 표시 / 마커 탭 시 이름·업데이트 시간·주소 오버레이 표시</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>TC-032</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>위치 공유 OFF 상태에서 지도 표시</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>F-011</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>위치 공유 OFF 상태에서 지도 표시</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>부모님이 위치 공유 OFF 상태 / 가족 구성원으로 로그인</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1. 가족 메인 화면 접속&lt;br&gt;2. 지도 및 안내 메시지 확인</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>1. 가족 메인 화면 접속
+2. 지도 및 안내 메시지 확인</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>부모님 위치 공유 상태: OFF</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>"부모님이 위치 공유를 꺼두셨습니다." 빈 지도 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>TC-033</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>마지막 위치 수신 후 5분 경과 시 마커 처리</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>F-011</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>마지막 위치 수신 후 5분 경과 시 마커 처리</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>가족 메인 화면에 부모님 마커가 표시된 상태 / 5분간 위치 업데이트 없음</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1. 부모님 위치 마커 표시 확인&lt;br&gt;2. 5분간 위치 데이터 전송 없음 (네트워크 차단 또는 대기)&lt;br&gt;3. 마커 상태 변화 확인</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 위치 마커 표시 확인
+2. 5분간 위치 데이터 전송 없음 (네트워크 차단 또는 대기)
+3. 마커 상태 변화 확인</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>마지막 위치 수신 후 경과 시간: 5분 이상</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>마커 회색 처리 / "위치 정보가 오래되었습니다." 배지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>TC-034</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>카카오맵 SDK 로드 실패 시 에러 화면 표시</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>F-011</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>카카오맵 SDK 로드 실패 시 에러 화면 표시</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>카카오맵 SDK 로드 실패 시뮬레이션 (API 키 무효화 또는 네트워크 차단)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1. KAKAO_MAP_API_KEY 를 무효값으로 설정&lt;br&gt;2. 가족 메인 화면 접속&lt;br&gt;3. 지도 영역 확인</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>1. KAKAO_MAP_API_KEY 를 무효값으로 설정
+2. 가족 메인 화면 접속
+3. 지도 영역 확인</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>카카오맵 SDK: 로드 실패</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>"지도를 불러오지 못했습니다." 에러 화면 표시</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TC-035</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>날짜 선택 후 위치 이력 정상 조회</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>F-012</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>날짜 선택 후 위치 이력 정상 조회</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>조회 날짜에 부모님 위치 이력 데이터 존재 / 가족 구성원 로그인</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1. 위치 이력 화면 접속&lt;br&gt;2. 캘린더에서 오늘 날짜 선택&lt;br&gt;3. 이동 경로 폴리라인 및 시간대별 목록 확인</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치 이력 화면 접속
+2. 캘린더에서 오늘 날짜 선택
+3. 이동 경로 폴리라인 및 시간대별 목록 확인</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>조회 날짜: 오늘 (위치 데이터 존재)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>카카오맵 폴리라인으로 이동 경로 표시 / 시작점(녹색)·종료점(빨간색) 마커 표시 / 시간대별 위치 목록 사이드 패널 표시</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>TC-036</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>7일 초과 날짜 선택 시도</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>F-012</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7일 초과 날짜 선택 시도</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>위치 이력 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1. 위치 이력 화면 캘린더 접속&lt;br&gt;2. 오늘 기준 8일 이전 날짜 선택 시도</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치 이력 화면 캘린더 접속
+2. 오늘 기준 8일 이전 날짜 선택 시도</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>조회 날짜: 오늘 - 8일</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>캘린더에서 7일 초과 날짜 선택 불가 처리 (비활성화)</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>TC-037</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>위치 데이터 없는 날짜 조회</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>F-012</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>위치 데이터 없는 날짜 조회</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>위치 데이터가 없는 날짜 존재</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1. 위치 이력 화면 접속&lt;br&gt;2. 위치 데이터가 없는 날짜 선택</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1. 위치 이력 화면 접속
+2. 위치 데이터가 없는 날짜 선택</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>조회 날짜: 위치 이력 없는 날</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>"해당 날짜의 이동 기록이 없습니다." 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>TC-038</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>GPS 좌표 역지오코딩 정상 변환</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>F-013</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>GPS 좌표 역지오코딩 정상 변환</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>카카오맵 Geocoding API 정상 연동 상태</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1. 가족 메인 화면에서 부모님 마커 탭&lt;br&gt;2. 오버레이에 표시되는 주소 확인</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>1. 가족 메인 화면에서 부모님 마커 탭
+2. 오버레이에 표시되는 주소 확인</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>위도: 37.5665, 경도: 126.9780</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>도로명 주소 텍스트 표시 (도로명 주소 없을 경우 지번 주소 표시)</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>TC-039</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>역지오코딩 API 호출 실패 시 대체 텍스트 표시</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>F-013</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>역지오코딩 API 호출 실패 시 대체 텍스트 표시</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>카카오맵 Geocoding API 응답 실패 시뮬레이션</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1. GET /api/location/address 강제 실패 설정&lt;br&gt;2. 가족 메인 화면에서 마커 탭&lt;br&gt;3. 주소 영역 표시 확인</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1. GET /api/location/address 강제 실패 설정
+2. 가족 메인 화면에서 마커 탭
+3. 주소 영역 표시 확인</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Geocoding API 응답: 실패</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>"위치 확인 중" 텍스트 표시</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>TC-040</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>SOS 버튼 탭 시 카운트다운 오버레이 표시</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>F-014</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SOS 버튼 탭 시 카운트다운 오버레이 표시</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>부모님 계정으로 로그인 / 부모님 메인 화면</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1. 부모님 메인 화면 중앙의 SOS 버튼(최소 80×80px) 확인&lt;br&gt;2. SOS 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 메인 화면 중앙의 SOS 버튼(최소 80×80px) 확인
+2. SOS 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>탭 이벤트: SOS 버튼</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>카운트다운 오버레이 즉시 표시 (반투명 레드 배경) / 버튼 scale 0.95 애니메이션 적용</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>TC-041</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>위치정보 동의 미완료 상태에서 SOS 발송</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>F-014</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>위치정보 동의 미완료 상태에서 SOS 발송</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>부모님 계정으로 로그인 / 위치정보 동의 미완료 상태</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1. 부모님 메인 화면 접속&lt;br&gt;2. SOS 버튼 탭 → 카운트다운 → 2초 경과</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 메인 화면 접속
+2. SOS 버튼 탭 → 카운트다운 → 2초 경과</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>위치정보 동의: 미완료</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>SOS 알림 발송 ("위치 불명" 상태) + 위치 정보 없음 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>TC-042</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2초 카운트다운 종료 후 SOS 발송 실행</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>F-015</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2초 카운트다운 종료 후 SOS 발송 실행</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>SOS 카운트다운 오버레이 표시 상태</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1. SOS 버튼 탭으로 카운트다운 오버레이 표시&lt;br&gt;2. 2초 경과 대기 (취소 없이)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1. SOS 버튼 탭으로 카운트다운 오버레이 표시
+2. 2초 경과 대기 (취소 없이)</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>경과 시간: 2초</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>카운트다운 0 도달 후 F-016(SOS 알림 발송) 자동 실행</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>TC-043</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>카운트다운 중 취소 버튼 탭</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>F-015</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>카운트다운 중 취소 버튼 탭</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>SOS 카운트다운 오버레이 표시 상태</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1. SOS 버튼 탭으로 카운트다운 오버레이 표시&lt;br&gt;2. 1초 이내에 취소 버튼 (48×48px 이상) 탭</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>1. SOS 버튼 탭으로 카운트다운 오버레이 표시
+2. 1초 이내에 취소 버튼 (48×48px 이상) 탭</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>탭 이벤트: 취소 버튼 (카운트다운 중)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>오버레이 즉시 제거 / 부모님 메인 화면 복귀 / SOS 알림 미발송</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>TC-044</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>카운트다운 중 화면 이탈 시 취소 처리</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>F-015</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>카운트다운 중 화면 이탈 시 취소 처리</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>SOS 카운트다운 오버레이 표시 상태</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1. SOS 카운트다운 오버레이 표시&lt;br&gt;2. 홈 버튼 탭 또는 브라우저 다른 탭으로 이동 (visibilitychange 이벤트 발생)&lt;br&gt;3. 서비스로 복귀 후 상태 확인</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>1. SOS 카운트다운 오버레이 표시
+2. 홈 버튼 탭 또는 브라우저 다른 탭으로 이동 (visibilitychange 이벤트 발생)
+3. 서비스로 복귀 후 상태 확인</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>화면 visibility 상태: hidden → visible</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>카운트다운 취소 처리 / SOS 알림 미발송 / 부모님 메인 화면 표시</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>TC-045</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SOS 확정 시 가족 전원 FCM 알림 정상 발송</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>F-016</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SOS 확정 시 가족 전원 FCM 알림 정상 발송</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 위치 공유 ON / 가족 그룹 구성원 FCM 토큰 정상 등록</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1. SOS 버튼 탭 → 2초 카운트다운 경과&lt;br&gt;2. POST /api/sos API 호출 확인&lt;br&gt;3. 가족 구성원 기기 FCM 알림 수신 확인&lt;br&gt;4. sos_events 테이블 저장 확인</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>1. SOS 버튼 탭 → 2초 카운트다운 경과
+2. POST /api/sos API 호출 확인
+3. 가족 구성원 기기 FCM 알림 수신 확인
+4. sos_events 테이블 저장 확인</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>user_id: 부모님 ID / group_id: 그룹 ID / 위치: 위도 37.5665, 경도 126.9780</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>3초 이내 가족 구성원 전원 FCM 알림 수신 / 부모님 화면에 "SOS를 보냈습니다." 완료 토스트 표시 / sos_events 테이블 저장</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TC-046</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>FCM 토큰 만료 토큰 발송 처리</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>F-016</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FCM 토큰 만료 토큰 발송 처리</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>가족 구성원 중 일부의 FCM 토큰이 만료된 상태</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>1. 만료된 FCM 토큰을 DB에 수동 설정&lt;br&gt;2. SOS 발송 실행&lt;br&gt;3. 서버 발송 결과 및 DB 확인</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>1. 만료된 FCM 토큰을 DB에 수동 설정
+2. SOS 발송 실행
+3. 서버 발송 결과 및 DB 확인</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>FCM 토큰: 만료된 토큰</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>만료 토큰 발송 실패 처리 / 해당 토큰 DB에서 삭제 / 나머지 유효 토큰 발송 정상 처리</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>TC-047</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>SOS 발송 중 네트워크 오류 발생</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>F-016</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SOS 발송 중 네트워크 오류 발생</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>SOS 발송 시 네트워크 오류 시뮬레이션</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1. POST /api/sos 요청 시 강제 네트워크 오류 설정&lt;br&gt;2. SOS 버튼 탭 → 카운트다운 → 발송 시도</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>1. POST /api/sos 요청 시 강제 네트워크 오류 설정
+2. SOS 버튼 탭 → 카운트다운 → 발송 시도</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>서버 응답: 네트워크 오류</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1회 재시도 후 실패 이력 저장 / 부모님에게 "전송 실패" 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>TC-048</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>위치 정보 없는 상태에서 SOS 발송</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>F-016</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>위치 정보 없는 상태에서 SOS 발송</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>부모님 위치정보 동의 미완료 또는 GPS 미수신 상태</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>1. 위치 데이터 없는 상태에서 SOS 발송 실행</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>위치 데이터: null</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>위치 정보 제외하고 "위치 불명" 텍스트로 FCM 알림 발송</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>TC-049</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>SOS 알림 탭 후 전화 연결 화면 이동</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>F-017</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>SOS 알림 탭 후 전화 연결 화면 이동</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>가족 구성원 기기에서 SOS FCM 알림 수신 상태</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1. 가족 구성원 기기에서 SOS FCM 알림 수신 확인&lt;br&gt;2. 알림 탭&lt;br&gt;3. 표시된 모달 및 전화 연결 버튼 확인</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>1. 가족 구성원 기기에서 SOS FCM 알림 수신 확인
+2. 알림 탭
+3. 표시된 모달 및 전화 연결 버튼 확인</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>FCM 알림 payload: 부모님 이름, 위치, 전화번호</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>SOS 수신 모달 표시 (부모님 이름, 위치, 전화 연결 버튼) / 전화 연결 버튼 탭 시 tel: scheme으로 네이티브 전화 앱 실행</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>TC-050</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>앱 종료 상태에서 SOS 알림 탭 후 재접속</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>F-017</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>앱 종료 상태에서 SOS 알림 탭 후 재접속</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>가족 구성원이 서비스를 종료한 상태에서 SOS 알림 수신</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1. 서비스 접속 종료 상태에서 SOS FCM 알림 수신&lt;br&gt;2. 알림 탭</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>1. 서비스 접속 종료 상태에서 SOS FCM 알림 수신
+2. 알림 탭</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>서비스 상태: 미접속 / FCM 알림 수신: 있음</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>서비스 재접속 후 SOS 수신 모달 자동 표시</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>TC-051</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>가족 채팅방 메시지 정상 전송 및 수신</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>F-018</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>가족 채팅방 메시지 정상 전송 및 수신</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>2명 이상의 가족 구성원이 채팅방에 접속 상태</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1. 채팅방 화면 접속&lt;br&gt;2. 메시지 입력 (100자 이내)&lt;br&gt;3. 전송 버튼 탭&lt;br&gt;4. 상대방 기기에서 메시지 수신 확인</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>1. 채팅방 화면 접속
+2. 메시지 입력 (100자 이내)
+3. 전송 버튼 탭
+4. 상대방 기기에서 메시지 수신 확인</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>메시지: "안녕하세요, 부모님 괜찮으신가요?"</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>채팅방에 말풍선 UI로 메시지 실시간 표시 / 상대방 기기에 즉시 수신</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>TC-052</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>500자 초과 메시지 전송 시도</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>F-018</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>500자 초과 메시지 전송 시도</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>채팅방 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1. 채팅방 입력 필드에 501자 이상 텍스트 붙여넣기&lt;br&gt;2. 전송 버튼 상태 확인</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>1. 채팅방 입력 필드에 501자 이상 텍스트 붙여넣기
+2. 전송 버튼 상태 확인</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>메시지: 501자 텍스트</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>입력 필드 하단 글자 수 카운터 표시 / 500자 초과 시 전송 버튼 비활성화</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>TC-053</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>WebSocket 5회 재연결 실패 시 안내 배너 표시</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>F-018</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>WebSocket 5회 재연결 실패 시 안내 배너 표시</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>채팅방 접속 상태 / WebSocket 연결 강제 차단</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1. 채팅방 접속 후 WebSocket 서버 연결 차단&lt;br&gt;2. 자동 재연결 5회 시도 대기 (exponential backoff: 1→2→4→8→16초)&lt;br&gt;3. 5회 실패 후 UI 확인</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>1. 채팅방 접속 후 WebSocket 서버 연결 차단
+2. 자동 재연결 5회 시도 대기 (exponential backoff: 1→2→4→8→16초)
+3. 5회 실패 후 UI 확인</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>WebSocket 재연결 시도: 5회 모두 실패</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>"채팅 연결이 끊겼습니다. 새로고침 해주세요." 안내 배너 표시</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>TC-054</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>이미지/파일 전송 시도 시 안내 메시지 표시</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>F-018</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>이미지/파일 전송 시도 시 안내 메시지 표시</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>채팅방 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>1. 채팅방 입력 영역에 이미지 파일 붙여넣기 또는 파일 첨부 시도</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>첨부 파일: 이미지 또는 문서 파일</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>"텍스트만 전송 가능합니다." 안내 메시지 표시 / 파일 전송 차단</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>TC-055</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>채팅방 미접속 구성원에게 FCM 푸시 알림 발송</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>F-019</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>채팅방 미접속 구성원에게 FCM 푸시 알림 발송</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>구성원 A는 채팅방 접속 / 구성원 B는 채팅방 미접속 또는 오프라인</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1. 구성원 A가 채팅 메시지 전송&lt;br&gt;2. 구성원 B 기기에서 FCM 알림 수신 확인</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>1. 구성원 A가 채팅 메시지 전송
+2. 구성원 B 기기에서 FCM 알림 수신 확인</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>메시지: "어디 계세요?" / 구성원 B 상태: 채팅방 미접속</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>구성원 B 기기에 발신자 이름 + 메시지 20자 미리보기 포함 FCM 알림 수신 / 알림 탭 시 채팅방 직접 진입</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>TC-056</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>채팅방 접속 중인 구성원에게 FCM 알림 미발송 확인</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>F-019</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>채팅방 접속 중인 구성원에게 FCM 알림 미발송 확인</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>구성원 A, B 모두 채팅방 접속 상태</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1. 구성원 A가 메시지 전송&lt;br&gt;2. 구성원 B 기기에서 FCM 알림 수신 여부 확인</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>1. 구성원 A가 메시지 전송
+2. 구성원 B 기기에서 FCM 알림 수신 여부 확인</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>구성원 B 상태: 채팅방 접속 중 (WebSocket 연결)</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>구성원 B 기기에 FCM 알림 미발송 / WebSocket으로만 메시지 수신</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>TC-057</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>안전 구역 정상 설정</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>F-020</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>안전 구역 정상 설정</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>가족 구성원 로그인 / Free 플랜 / 기존 안전 구역 0개</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1. 안전 구역 설정 화면 접속&lt;br&gt;2. 카카오맵에서 중심점 탭 선택&lt;br&gt;3. 구역명 입력 (예: "우리 집")&lt;br&gt;4. 반경 슬라이더 조정 (500m)&lt;br&gt;5. 저장 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>1. 안전 구역 설정 화면 접속
+2. 카카오맵에서 중심점 탭 선택
+3. 구역명 입력 (예: "우리 집")
+4. 반경 슬라이더 조정 (500m)
+5. 저장 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>구역명: "우리 집" / 중심 좌표: 위도 37.5665, 경도 126.9780 / 반경: 500m</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>지도에 반투명 원형 오버레이 표시 / 구역 목록에 추가 / F-021 이탈 감지 활성화</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>TC-058</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Free 플랜 구역 한도 초과 등록 시도</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>F-020</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Free 플랜 구역 한도 초과 등록 시도</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Free 플랜 사용 중 / 이미 1개의 안전 구역 등록된 상태</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>1. 안전 구역 설정 화면에서 추가 구역 등록 시도</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>현재 등록 구역 수: 1개 (Free 플랜 한도)</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>"Pro 플랜에서 최대 2개 구역을 설정할 수 있습니다." 업그레이드 유도 안내 메시지 표시</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>TC-059</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>중심점 미지정 상태에서 저장 시도</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>F-020</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>중심점 미지정 상태에서 저장 시도</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>안전 구역 설정 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1. 구역명 입력&lt;br&gt;2. 반경 설정&lt;br&gt;3. 지도에서 중심점 지정 없이 저장 버튼 상태 확인</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>1. 구역명 입력
+2. 반경 설정
+3. 지도에서 중심점 지정 없이 저장 버튼 상태 확인</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>중심점 좌표: 미지정</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>저장 버튼 비활성화 / 탭해도 API 요청 미전송</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>TC-060</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>부모님 안전 구역 이탈 감지 및 알림 발송</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>F-021</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>부모님 안전 구역 이탈 감지 및 알림 발송</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>안전 구역 1개 설정 완료 / 부모님 위치 공유 ON</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1. 부모님이 설정된 안전 구역 내부에 위치&lt;br&gt;2. 부모님 위치를 안전 구역 반경 외부로 이동 시뮬레이션&lt;br&gt;3. 가족 구성원 FCM 알림 수신 확인</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님이 설정된 안전 구역 내부에 위치
+2. 부모님 위치를 안전 구역 반경 외부로 이동 시뮬레이션
+3. 가족 구성원 FCM 알림 수신 확인</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>부모님 위치: 안전 구역 반경 외부 (이탈 상태 30초 이상 연속)</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>60초 이내 가족 전원에게 FCM 알림 발송 ("부모님이 [구역명]을 벗어났습니다.") / geofence_events 테이블 이력 저장</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>TC-061</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>부모님 안전 구역 복귀 감지 및 알림 발송</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>F-021</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>부모님 안전 구역 복귀 감지 및 알림 발송</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>부모님이 안전 구역 이탈 상태</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1. 부모님이 안전 구역 외부에 위치&lt;br&gt;2. 부모님 위치를 안전 구역 내부로 이동 시뮬레이션&lt;br&gt;3. 가족 구성원 FCM 알림 확인</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님이 안전 구역 외부에 위치
+2. 부모님 위치를 안전 구역 내부로 이동 시뮬레이션
+3. 가족 구성원 FCM 알림 확인</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>부모님 위치: 안전 구역 반경 내부 (복귀)</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>가족 전원에게 FCM 알림 발송 ("부모님이 [구역명]으로 돌아오셨습니다.")</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>TC-062</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>GPS 오차로 인한 경계 근처 진동 방지 처리</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>F-021</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>GPS 오차로 인한 경계 근처 진동 방지 처리</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>부모님이 안전 구역 경계 100m 버퍼 존 내에 위치</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1. 부모님 위치를 경계 근처에서 반복적으로 내부/외부로 변경 시뮬레이션 (진동)&lt;br&gt;2. FCM 알림 발송 여부 확인</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>1. 부모님 위치를 경계 근처에서 반복적으로 내부/외부로 변경 시뮬레이션 (진동)
+2. FCM 알림 발송 여부 확인</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>부모님 위치: 경계선 ± 50m 내 반복 이동</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>30초 연속 이탈이 확인된 경우에만 알림 발송 (진동 상태에서 알림 미발송)</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>TC-063</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>관리자 그룹 목록 정상 조회</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>F-022</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>관리자 그룹 목록 정상 조회</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>관리자(admin) 역할로 로그인</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1. 관리자 회원 목록 화면 접속&lt;br&gt;2. 그룹 목록 표시 확인&lt;br&gt;3. 검색어 입력 및 정렬 기준 변경 테스트</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 회원 목록 화면 접속
+2. 그룹 목록 표시 확인
+3. 검색어 입력 및 정렬 기준 변경 테스트</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>검색어: "우리 가족" / 정렬: 생성일 기준 내림차순 / 페이지: 1</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>가족 그룹 목록 테이블 표시 (그룹명, 생성일, 구성원 수, 마지막 활동일) / 페이지당 20건</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>TC-064</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>비관리자 계정으로 관리자 화면 접근 시도</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>F-022</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>비관리자 계정으로 관리자 화면 접근 시도</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>일반 사용자(family 또는 parent) 역할로 로그인</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>1. 관리자 화면 URL 직접 접속 시도 (/admin/...)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>사용자 역할: family</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorized 반환 / 로그인 화면으로 이동</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>TC-065</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>등록 그룹 없는 상태에서 목록 조회</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>F-022</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>등록 그룹 없는 상태에서 목록 조회</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / DB에 가족 그룹 데이터 없음</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>1. 관리자 회원 목록 화면 접속&lt;br&gt;2. 목록 영역 확인</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 회원 목록 화면 접속
+2. 목록 영역 확인</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>groups 테이블 레코드 수: 0</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>"등록된 그룹이 없습니다." 빈 상태 화면 표시</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>TC-066</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>특정 그룹 상세 정보 정상 조회</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>F-023</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>특정 그룹 상세 정보 정상 조회</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / 조회할 그룹이 존재</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>1. 관리자 그룹 목록에서 특정 그룹 선택&lt;br&gt;2. 그룹 상세 화면 표시 확인</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 그룹 목록에서 특정 그룹 선택
+2. 그룹 상세 화면 표시 확인</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>group_id: 유효한 그룹 ID</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>구성원 카드 목록 표시 (이름, 역할, 마지막 접속, 위치 공유 상태)</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>TC-067</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>존재하지 않는 그룹 ID로 상세 조회 시도</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>F-023</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>존재하지 않는 그룹 ID로 상세 조회 시도</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>1. 존재하지 않는 group_id로 API 직접 호출 (GET /api/admin/groups/99999)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>group_id: 99999 (미존재)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>404 Not Found 반환 / 그룹 목록 화면으로 복귀</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>TC-068</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>관리자 SMS 정상 발송</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>F-024</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>관리자 SMS 정상 발송</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / NHN Cloud SMS API 연동 정상</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1. 관리자 SMS 발송 화면 접속&lt;br&gt;2. 수신 대상 개별 선택 (체크박스)&lt;br&gt;3. 메시지 내용 입력 (80자 이내)&lt;br&gt;4. 발송 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 SMS 발송 화면 접속
+2. 수신 대상 개별 선택 (체크박스)
+3. 메시지 내용 입력 (80자 이내)
+4. 발송 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>수신 대상: 1명 선택 / 메시지: "안녕하세요. 서비스 점검 안내드립니다." (30자)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>SMS 발송 완료 토스트 ("총 1건 발송 완료") / sms_logs 테이블 발송 이력 저장</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>TC-069</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>수신 대상 미선택 상태에서 발송 시도</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>F-024</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>수신 대상 미선택 상태에서 발송 시도</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>관리자 SMS 발송 화면 접속 상태</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1. 수신 대상 선택 없이 메시지 입력&lt;br&gt;2. 발송 버튼 상태 확인</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>1. 수신 대상 선택 없이 메시지 입력
+2. 발송 버튼 상태 확인</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>수신 대상: 0명</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>발송 버튼 비활성화</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>TC-070</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>NHN Cloud SMS API 오류 시 처리</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>F-024</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>NHN Cloud SMS API 오류 시 처리</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>NHN Cloud SMS API 강제 오류 응답 설정</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1. 수신 대상 및 메시지 설정 후 발송&lt;br&gt;2. API 오류 응답 수신</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>1. 수신 대상 및 메시지 설정 후 발송
+2. API 오류 응답 수신</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>NHN Cloud SMS API 응답: 오류 코드 포함 실패 응답</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>오류 코드 포함 에러 토스트 표시 / 발송 실패 이력 sms_logs에 저장</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>TC-071</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>관리자 카카오 알림톡 정상 발송</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>F-025</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>관리자 카카오 알림톡 정상 발송</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / 카카오 알림톡 API 정상 연동 / 발송 템플릿 등록 완료</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>1. 관리자 알림톡 발송 화면 접속&lt;br&gt;2. 발송 대상 선택&lt;br&gt;3. 알림톡 템플릿 선택&lt;br&gt;4. 변수 값 입력&lt;br&gt;5. 발송 버튼 탭</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 알림톡 발송 화면 접속
+2. 발송 대상 선택
+3. 알림톡 템플릿 선택
+4. 변수 값 입력
+5. 발송 버튼 탭</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>템플릿: 서비스 안내 템플릿 / 변수: 사용자 이름</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>발송 완료 메시지 표시 / alimtalk_logs 테이블 저장 (성공 N건 / 실패 N건)</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>TC-072</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>월 발송 한도 초과 시 처리</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>F-025</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>월 발송 한도 초과 시 처리</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>이번 달 알림톡 발송 한도에 도달한 상태</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1. 알림톡 발송 시도&lt;br&gt;2. 월 한도 초과 응답 확인</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>1. 알림톡 발송 시도
+2. 월 한도 초과 응답 확인</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>알림톡 API 응답: 월 한도 초과</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>한도 경고 메시지 표시 후 발송 중단</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>TC-073</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>알림톡 발송 실패 건 재발송</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>F-025</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>알림톡 발송 실패 건 재발송</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>이전 발송에서 일부 실패 이력이 존재</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>1. 알림톡 발송 이력 화면 접속&lt;br&gt;2. 실패 건 재발송 버튼 탭&lt;br&gt;3. 재발송 결과 확인</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>1. 알림톡 발송 이력 화면 접속
+2. 실패 건 재발송 버튼 탭
+3. 재발송 결과 확인</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>재발송 대상: 실패 이력 건</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>실패 건 재발송 처리 / 발송 결과 이력 갱신</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>TC-074</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>관리자 통계 대시보드 정상 조회</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>F-026</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>관리자 통계 대시보드 정상 조회</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / 통계 데이터 존재</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1. 관리자 통계 대시보드 접속&lt;br&gt;2. 기간 선택 (일별)&lt;br&gt;3. 지표 카드, 추이 차트, 데이터 테이블 확인</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>1. 관리자 통계 대시보드 접속
+2. 기간 선택 (일별)
+3. 지표 카드, 추이 차트, 데이터 테이블 확인</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>기간: 일별 / 지표: DAU, SOS 발생 건수</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>지표 카드 (요약 수치) + 라인/바 차트 + 데이터 테이블 정상 표시</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>TC-075</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>데이터 없는 기간 통계 조회</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>F-026</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>데이터 없는 기간 통계 조회</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>1. 통계 대시보드에서 데이터 없는 과거 기간 선택</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>기간: 데이터 미존재 날짜 범위</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>빈 차트 표시 + "해당 기간의 데이터가 없습니다." 안내 메시지</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>TC-076</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>통계 데이터 CSV 내보내기</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>F-026</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>통계 데이터 CSV 내보내기</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>관리자 로그인 / 통계 데이터 존재</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>1. 통계 대시보드에서 기간 및 지표 선택&lt;br&gt;2. CSV 내보내기 버튼 탭&lt;br&gt;3. 파일 다운로드 확인</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>1. 통계 대시보드에서 기간 및 지표 선택
+2. CSV 내보내기 버튼 탭
+3. 파일 다운로드 확인</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>기간: 최근 7일 / 지표: 전체</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>CSV 파일 다운로드 실행 / 파일 내 집계 데이터 정상 포함</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>TC-077</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>배터리 절약 모드 전환 (30초 → 3분)</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>F-027</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>배터리 절약 모드 전환 (30초 → 3분)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 일반 모드 (30초 간격) 상태</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1. 설정 화면 접속&lt;br&gt;2. 배터리 절약 모드 토글 활성화&lt;br&gt;3. 위치 전송 간격 변경 확인</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>1. 설정 화면 접속
+2. 배터리 절약 모드 토글 활성화
+3. 위치 전송 간격 변경 확인</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>설정: 배터리 절약 모드 ON</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>위치 전송 간격 3분(180초)으로 변경 / users 테이블 location_interval 필드 180 저장 / 설정 화면에 현재 모드 표시 + 예상 절약 효과 안내 텍스트</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>TC-078</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>일반 모드 전환 (3분 → 30초)</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>F-027</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>일반 모드 전환 (3분 → 30초)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>부모님 계정 로그인 / 배터리 절약 모드 (3분 간격) 상태</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1. 설정 화면 접속&lt;br&gt;2. 배터리 절약 모드 토글 비활성화 (일반 모드 전환)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>1. 설정 화면 접속
+2. 배터리 절약 모드 토글 비활성화 (일반 모드 전환)</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>설정: 배터리 절약 모드 OFF</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>위치 전송 간격 30초로 변경 / users 테이블 location_interval 필드 30 저장</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>TC-079</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>개인정보처리방침 페이지 정상 접근</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>F-028</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>개인정보처리방침 페이지 정상 접근</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>서비스 접속 상태 (로그인 여부 무관)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1. 회원가입 화면 또는 설정 화면에서 개인정보처리방침 링크 탭&lt;br&gt;2. /privacy 페이지 또는 모달 표시 확인&lt;br&gt;3. 콘텐츠 구성 확인</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>1. 회원가입 화면 또는 설정 화면에서 개인정보처리방침 링크 탭
+2. /privacy 페이지 또는 모달 표시 확인
+3. 콘텐츠 구성 확인</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>경로: /privacy</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>처리방침 전문 정상 표시 / 항목 포함 확인: 수집 개인정보 항목, 수집 목적, 보유·이용 기간, 제3자 제공, 위치정보 수집·이용 동의</t>
         </is>
       </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>(테스트 실행 후 기입)</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Pass / Fail</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>